--- a/artfynd/Stor-Svartliden artfynd.xlsx
+++ b/artfynd/Stor-Svartliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16944515</v>
+        <v>56623471</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676842</v>
+        <v>676263</v>
       </c>
       <c r="R2" t="n">
-        <v>7121216</v>
+        <v>7121068</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,62 +757,52 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16944552</v>
+        <v>56623472</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676967</v>
+        <v>676058</v>
       </c>
       <c r="R3" t="n">
-        <v>7120870</v>
+        <v>7121112</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,45 +859,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56623483</v>
+        <v>56623488</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676058</v>
+        <v>676239</v>
       </c>
       <c r="R4" t="n">
-        <v>7121112</v>
+        <v>7120951</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16944994</v>
+        <v>56623489</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676936</v>
+        <v>676055</v>
       </c>
       <c r="R5" t="n">
-        <v>7120920</v>
+        <v>7121083</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,40 +1063,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>16944761</v>
+        <v>56623491</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1118,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677163</v>
+        <v>676058</v>
       </c>
       <c r="R6" t="n">
-        <v>7120894</v>
+        <v>7121112</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,62 +1165,52 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16944622</v>
+        <v>56623492</v>
       </c>
       <c r="B7" t="n">
-        <v>80119</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>677454</v>
+        <v>676124</v>
       </c>
       <c r="R7" t="n">
-        <v>7121421</v>
+        <v>7120946</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,40 +1267,30 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56623481</v>
+        <v>56623479</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676053</v>
+        <v>676124</v>
       </c>
       <c r="R8" t="n">
-        <v>7121073</v>
+        <v>7120946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16944554</v>
+        <v>56623481</v>
       </c>
       <c r="B9" t="n">
-        <v>91259</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677122</v>
+        <v>676053</v>
       </c>
       <c r="R9" t="n">
-        <v>7121243</v>
+        <v>7121073</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,45 +1471,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # låga</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67478964</v>
+        <v>56623483</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>676451</v>
+        <v>676058</v>
       </c>
       <c r="R10" t="n">
-        <v>7121619</v>
+        <v>7121112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,12 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-06-13</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-06-13</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,26 +1572,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sören Uppsäll</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sören Uppsäll, Per Nihlén</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56623489</v>
+        <v>56623470</v>
       </c>
       <c r="B11" t="n">
-        <v>80084</v>
+        <v>89292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1604,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>676055</v>
+        <v>676435</v>
       </c>
       <c r="R11" t="n">
-        <v>7121083</v>
+        <v>7121409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1677,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1760,32 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16944443</v>
+        <v>67478964</v>
       </c>
       <c r="B12" t="n">
-        <v>91819</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,13 +1730,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>676938</v>
+        <v>676451</v>
       </c>
       <c r="R12" t="n">
-        <v>7120915</v>
+        <v>7121619</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,12 +1760,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1841,80 +1776,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7125391</v>
+        <v>67478970</v>
       </c>
       <c r="B13" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677913</v>
+        <v>676483</v>
       </c>
       <c r="R13" t="n">
-        <v>7120569</v>
+        <v>7121619</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,17 +1857,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33673</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1966,61 +1877,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Sören Uppsäll</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Per Nihlén, Sören Uppsäll</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7128044</v>
+        <v>126777279</v>
       </c>
       <c r="B14" t="n">
-        <v>80112</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Västra Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677912</v>
+        <v>677053</v>
       </c>
       <c r="R14" t="n">
-        <v>7120566</v>
+        <v>7121108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,17 +1954,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33674</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,26 +1970,41 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126777279</v>
+        <v>16944433</v>
       </c>
       <c r="B15" t="n">
-        <v>79012</v>
+        <v>89292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,37 +2012,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västra Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>677053</v>
+        <v>676838</v>
       </c>
       <c r="R15" t="n">
-        <v>7121108</v>
+        <v>7121169</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,22 +2101,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16945127</v>
+        <v>16944434</v>
       </c>
       <c r="B16" t="n">
-        <v>79012</v>
+        <v>89292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>677610</v>
+        <v>676918</v>
       </c>
       <c r="R16" t="n">
-        <v>7120607</v>
+        <v>7121025</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,6 +2194,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2293,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56623491</v>
+        <v>16944443</v>
       </c>
       <c r="B17" t="n">
-        <v>80084</v>
+        <v>92509</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>676058</v>
+        <v>676938</v>
       </c>
       <c r="R17" t="n">
-        <v>7121112</v>
+        <v>7120915</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2375,68 +2307,78 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126777280</v>
+        <v>16944552</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västra Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>676990</v>
+        <v>676967</v>
       </c>
       <c r="R18" t="n">
-        <v>7121443</v>
+        <v>7120870</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2460,12 +2402,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,68 +2429,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16944885</v>
+        <v>126777278</v>
       </c>
       <c r="B19" t="n">
-        <v>79987</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Västra Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>677454</v>
+        <v>677053</v>
       </c>
       <c r="R19" t="n">
-        <v>7121421</v>
+        <v>7121108</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2572,12 +2519,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,60 +2538,60 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56623488</v>
+        <v>16944994</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2654,13 +2601,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>676239</v>
+        <v>676936</v>
       </c>
       <c r="R20" t="n">
-        <v>7120951</v>
+        <v>7120920</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2701,68 +2648,78 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16944434</v>
+        <v>126777280</v>
       </c>
       <c r="B21" t="n">
-        <v>88654</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Västra Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>676918</v>
+        <v>676990</v>
       </c>
       <c r="R21" t="n">
-        <v>7121025</v>
+        <v>7121443</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2786,12 +2743,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2821,22 +2778,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56623470</v>
+        <v>16945127</v>
       </c>
       <c r="B22" t="n">
-        <v>88654</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,13 +2825,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>676435</v>
+        <v>677610</v>
       </c>
       <c r="R22" t="n">
-        <v>7121409</v>
+        <v>7120607</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2914,69 +2871,64 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7122228</v>
+        <v>16944553</v>
       </c>
       <c r="B23" t="n">
-        <v>98281</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>223597</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>677951</v>
+        <v>677424</v>
       </c>
       <c r="R23" t="n">
-        <v>7120611</v>
+        <v>7120793</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3000,17 +2952,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33672</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,48 +2968,68 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>låga</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # låga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16944621</v>
+        <v>16944554</v>
       </c>
       <c r="B24" t="n">
-        <v>80119</v>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>677366</v>
+        <v>677122</v>
       </c>
       <c r="R24" t="n">
-        <v>7120618</v>
+        <v>7121243</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3121,17 +3088,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>låga</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies # låga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3149,10 +3121,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>56623479</v>
+        <v>16944761</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,13 +3156,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>676124</v>
+        <v>677163</v>
       </c>
       <c r="R25" t="n">
-        <v>7120946</v>
+        <v>7120894</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,52 +3203,62 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>56623472</v>
+        <v>16944762</v>
       </c>
       <c r="B26" t="n">
-        <v>91819</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3286,13 +3268,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>676058</v>
+        <v>677366</v>
       </c>
       <c r="R26" t="n">
-        <v>7121112</v>
+        <v>7120618</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,30 +3315,40 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7120347</v>
+        <v>16944424</v>
       </c>
       <c r="B27" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,24 +3373,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>677992</v>
+        <v>677163</v>
       </c>
       <c r="R27" t="n">
-        <v>7120515</v>
+        <v>7120894</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3422,17 +3410,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2012-06-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33671</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3443,48 +3426,63 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16944516</v>
+        <v>16944621</v>
       </c>
       <c r="B28" t="n">
-        <v>91263</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3494,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>677434</v>
+        <v>677366</v>
       </c>
       <c r="R28" t="n">
-        <v>7121446</v>
+        <v>7120618</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3543,17 +3541,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3571,48 +3569,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126777278</v>
+        <v>16944885</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>80336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Västra Vargträsk, Ly lm</t>
+          <t>Stor-Svartliden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>677053</v>
+        <v>677454</v>
       </c>
       <c r="R29" t="n">
-        <v>7121108</v>
+        <v>7121421</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3636,12 +3634,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,60 +3653,60 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16944433</v>
+        <v>16944622</v>
       </c>
       <c r="B30" t="n">
-        <v>88654</v>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3718,10 +3716,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>676838</v>
+        <v>677454</v>
       </c>
       <c r="R30" t="n">
-        <v>7121169</v>
+        <v>7121421</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3767,17 +3765,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3795,45 +3793,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56623471</v>
+        <v>7128044</v>
       </c>
       <c r="B31" t="n">
-        <v>91819</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>676263</v>
+        <v>677912</v>
       </c>
       <c r="R31" t="n">
-        <v>7121068</v>
+        <v>7120566</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,12 +3862,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33674</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3876,31 +3883,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16944424</v>
+        <v>7120347</v>
       </c>
       <c r="B32" t="n">
-        <v>80118</v>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3925,20 +3927,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>677163</v>
+        <v>677992</v>
       </c>
       <c r="R32" t="n">
-        <v>7120894</v>
+        <v>7120515</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3962,12 +3968,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33671</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3978,76 +3989,65 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>56623492</v>
+        <v>7125391</v>
       </c>
       <c r="B33" t="n">
-        <v>80084</v>
+        <v>80468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>676124</v>
+        <v>677913</v>
       </c>
       <c r="R33" t="n">
-        <v>7120946</v>
+        <v>7120569</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,12 +4074,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33673</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4090,69 +4095,64 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16944553</v>
+        <v>7122228</v>
       </c>
       <c r="B34" t="n">
-        <v>91259</v>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>223597</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stor-Svartliden, Ly lm</t>
+          <t>Vargträsk, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>677424</v>
+        <v>677951</v>
       </c>
       <c r="R34" t="n">
-        <v>7120793</v>
+        <v>7120611</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4176,12 +4176,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2014-09-26</t>
+          <t>2012-06-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Oskar Wallströmer  ID;33672</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4192,151 +4197,19 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>låga</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # låga</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>16944762</v>
-      </c>
-      <c r="B35" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Stor-Svartliden, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>677366</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7120618</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Örträsk</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2014-09-26</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
